--- a/artfynd/A 22563-2025 artfynd.xlsx
+++ b/artfynd/A 22563-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>121151032</v>
       </c>
       <c r="B2" t="n">
-        <v>92005</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -786,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121151030</v>
+        <v>121151045</v>
       </c>
       <c r="B3" t="n">
-        <v>92018</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>232140</v>
+        <v>2059</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>744865</v>
+        <v>744825</v>
       </c>
       <c r="R3" t="n">
-        <v>7320548</v>
+        <v>7320125</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,12 +850,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -897,37 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121151049</v>
+        <v>121152783</v>
       </c>
       <c r="B4" t="n">
-        <v>92017</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>744913</v>
+        <v>744730</v>
       </c>
       <c r="R4" t="n">
-        <v>7320099</v>
+        <v>7320180</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,15 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121151020</v>
+        <v>121151051</v>
       </c>
       <c r="B5" t="n">
-        <v>92017</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1024,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5449</v>
+        <v>3100</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>744714</v>
+        <v>745021</v>
       </c>
       <c r="R5" t="n">
-        <v>7320707</v>
+        <v>7320187</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1082,12 +1062,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1119,15 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121151033</v>
+        <v>121151026</v>
       </c>
       <c r="B6" t="n">
-        <v>78343</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1135,21 +1110,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>744897</v>
+        <v>744833</v>
       </c>
       <c r="R6" t="n">
-        <v>7320523</v>
+        <v>7320585</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1230,37 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121151035</v>
+        <v>121151038</v>
       </c>
       <c r="B7" t="n">
-        <v>91993</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4365</v>
+        <v>4362</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>744916</v>
+        <v>744908</v>
       </c>
       <c r="R7" t="n">
-        <v>7320507</v>
+        <v>7320534</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1341,19 +1311,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121151028</v>
+        <v>121151024</v>
       </c>
       <c r="B8" t="n">
-        <v>91989</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1385,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>744864</v>
+        <v>744791</v>
       </c>
       <c r="R8" t="n">
-        <v>7320552</v>
+        <v>7320642</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1452,15 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121151052</v>
+        <v>121151028</v>
       </c>
       <c r="B9" t="n">
-        <v>78343</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,21 +1428,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1496,10 +1456,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>745069</v>
+        <v>744864</v>
       </c>
       <c r="R9" t="n">
-        <v>7320182</v>
+        <v>7320552</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1526,12 +1486,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1563,37 +1523,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121151021</v>
+        <v>121151050</v>
       </c>
       <c r="B10" t="n">
-        <v>89391</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6276</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1607,10 +1562,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>744656</v>
+        <v>744913</v>
       </c>
       <c r="R10" t="n">
-        <v>7320762</v>
+        <v>7320099</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1637,12 +1592,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1674,37 +1629,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121151022</v>
+        <v>121151035</v>
       </c>
       <c r="B11" t="n">
-        <v>92001</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4366</v>
+        <v>4365</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1718,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>744660</v>
+        <v>744916</v>
       </c>
       <c r="R11" t="n">
-        <v>7320759</v>
+        <v>7320507</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1785,15 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121151048</v>
+        <v>121151022</v>
       </c>
       <c r="B12" t="n">
-        <v>92017</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1801,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5449</v>
+        <v>4366</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1829,10 +1774,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>744910</v>
+        <v>744660</v>
       </c>
       <c r="R12" t="n">
-        <v>7320115</v>
+        <v>7320759</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1859,12 +1804,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1896,15 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121151038</v>
+        <v>121151037</v>
       </c>
       <c r="B13" t="n">
-        <v>91983</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1912,21 +1852,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1940,10 +1880,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>744908</v>
+        <v>744909</v>
       </c>
       <c r="R13" t="n">
-        <v>7320534</v>
+        <v>7320532</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2007,37 +1947,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121151037</v>
+        <v>121151046</v>
       </c>
       <c r="B14" t="n">
-        <v>92001</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4366</v>
+        <v>4745</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2051,10 +1986,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>744909</v>
+        <v>744825</v>
       </c>
       <c r="R14" t="n">
-        <v>7320532</v>
+        <v>7320125</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2081,12 +2016,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2118,37 +2053,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121151024</v>
+        <v>121151018</v>
       </c>
       <c r="B15" t="n">
-        <v>91989</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>5448</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2162,10 +2092,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>744791</v>
+        <v>745153</v>
       </c>
       <c r="R15" t="n">
-        <v>7320642</v>
+        <v>7320193</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2229,37 +2159,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121151026</v>
+        <v>121151021</v>
       </c>
       <c r="B16" t="n">
-        <v>91981</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90691</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4361</v>
+        <v>6276</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2273,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>744833</v>
+        <v>744656</v>
       </c>
       <c r="R16" t="n">
-        <v>7320585</v>
+        <v>7320762</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2340,15 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121151051</v>
+        <v>121151033</v>
       </c>
       <c r="B17" t="n">
-        <v>92014</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2356,21 +2276,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3100</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2384,10 +2304,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>745021</v>
+        <v>744897</v>
       </c>
       <c r="R17" t="n">
-        <v>7320187</v>
+        <v>7320523</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2414,12 +2334,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2451,37 +2371,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121151050</v>
+        <v>121151044</v>
       </c>
       <c r="B18" t="n">
-        <v>91989</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2495,10 +2410,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>744913</v>
+        <v>744823</v>
       </c>
       <c r="R18" t="n">
-        <v>7320099</v>
+        <v>7320120</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2559,6 +2474,324 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>121151052</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Vitberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>745069</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7320182</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>121151030</v>
+      </c>
+      <c r="B20" t="n">
+        <v>93228</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Vitberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>744865</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7320548</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>121151047</v>
+      </c>
+      <c r="B21" t="n">
+        <v>93228</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Vitberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>744825</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7320125</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22563-2025 artfynd.xlsx
+++ b/artfynd/A 22563-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121151032</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121151045</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121152783</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121151051</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121151026</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121151038</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,6 +1449,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121151024</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1520,6 +1560,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121151028</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1626,6 +1671,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121151050</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1732,6 +1782,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121151035</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1838,6 +1893,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121151022</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1944,6 +2004,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121151037</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2050,6 +2115,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121151046</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2156,6 +2226,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121151018</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2262,6 +2337,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121151021</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2368,6 +2448,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121151033</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2474,6 +2559,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121151044</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2580,6 +2670,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121151052</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2686,6 +2781,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121151030</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2792,8 +2892,35 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121151047</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>